--- a/public/Handover Tamplate New.xlsx
+++ b/public/Handover Tamplate New.xlsx
@@ -1973,105 +1973,156 @@
     <col min="2" max="2" width="76.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>Project_Department</v>
+      </c>
+      <c r="B1" t="s">
+        <v/>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="13"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>Handover_Date</v>
+      </c>
+      <c r="B2" t="s">
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>Project_Counteragent_Entity_Type</v>
+      </c>
+      <c r="B3" t="s">
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="15"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>Project_Counteragent_Name</v>
+      </c>
+      <c r="B4" t="s">
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>Project_Counteragent_Director_Genitive</v>
+      </c>
+      <c r="B5" t="s">
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="12"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>Project_Counteragent_Director</v>
+      </c>
+      <c r="B6" t="s">
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>Project_Counteragent_Address_Line_1</v>
+      </c>
+      <c r="B7" t="s">
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>Project_Counteragent_Address_Line_2</v>
+      </c>
+      <c r="B8" t="s">
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="12"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>Project_Counteragent_ID</v>
+      </c>
+      <c r="B9" t="s">
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>Project_Address</v>
+      </c>
+      <c r="B10" t="s">
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>Project_Insider_Entity_Type</v>
+      </c>
+      <c r="B11" t="s">
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>Project_Insider_Name</v>
+      </c>
+      <c r="B12" t="s">
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>Project_Insider_ID</v>
+      </c>
+      <c r="B13" t="s">
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>Project_Insider_Address_Line1</v>
+      </c>
+      <c r="B14" t="s">
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="15"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>Project_Insider_Address_Line2</v>
+      </c>
+      <c r="B15" t="s">
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>Project_Insider_Director_Genitive</v>
+      </c>
+      <c r="B16" t="s">
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="15"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>Project_Insider_Director</v>
+      </c>
+      <c r="B17" t="s">
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>Contract_Date</v>
+      </c>
+      <c r="B18" t="s">
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>Project_Currency</v>
+      </c>
+      <c r="B19" t="s">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/public/Handover Tamplate New.xlsx
+++ b/public/Handover Tamplate New.xlsx
@@ -1973,156 +1973,105 @@
     <col min="2" max="2" width="76.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>Project_Department</v>
-      </c>
-      <c r="B1" t="s">
-        <v/>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>Handover_Date</v>
-      </c>
-      <c r="B2" t="s">
-        <v/>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>12</v>
+      </c>
+      <c r="B2" s="13"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>Project_Counteragent_Entity_Type</v>
-      </c>
-      <c r="B3" t="s">
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>Project_Counteragent_Name</v>
-      </c>
-      <c r="B4" t="s">
-        <v/>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>Project_Counteragent_Director_Genitive</v>
-      </c>
-      <c r="B5" t="s">
-        <v/>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="15"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>Project_Counteragent_Director</v>
-      </c>
-      <c r="B6" t="s">
-        <v/>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>17</v>
+      </c>
+      <c r="E6" s="12"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>Project_Counteragent_Address_Line_1</v>
-      </c>
-      <c r="B7" t="s">
-        <v/>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>Project_Counteragent_Address_Line_2</v>
-      </c>
-      <c r="B8" t="s">
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>Project_Counteragent_ID</v>
-      </c>
-      <c r="B9" t="s">
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>18</v>
+      </c>
+      <c r="B9" s="12"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>Project_Address</v>
-      </c>
-      <c r="B10" t="s">
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>Project_Insider_Entity_Type</v>
-      </c>
-      <c r="B11" t="s">
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>Project_Insider_Name</v>
-      </c>
-      <c r="B12" t="s">
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>Project_Insider_ID</v>
-      </c>
-      <c r="B13" t="s">
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>Project_Insider_Address_Line1</v>
-      </c>
-      <c r="B14" t="s">
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>Project_Insider_Address_Line2</v>
-      </c>
-      <c r="B15" t="s">
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>Project_Insider_Director_Genitive</v>
-      </c>
-      <c r="B16" t="s">
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="15"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>Project_Insider_Director</v>
-      </c>
-      <c r="B17" t="s">
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>Contract_Date</v>
-      </c>
-      <c r="B18" t="s">
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="15"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>Project_Currency</v>
-      </c>
-      <c r="B19" t="s">
-        <v/>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
